--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3860" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:02+00:00</t>
+    <t>2026-06-29T12:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -274,7 +274,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}fr-encounter-status:Le statut de la rencontre doit être 'finished' (rencontre réalisée), 'planned' (rencontre planifiée) ou 'proposed' (rencontre prévue mais non confirmée). {status = 'finished' or status = 'planned' or status = 'proposed'}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -859,7 +859,7 @@
     <t>Encounter.status</t>
   </si>
   <si>
-    <t>Statut de la rencontre (finished | planned | proposed)</t>
+    <t>Statut de la rencontre (finished | planned | proposed | ...)</t>
   </si>
   <si>
     <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
@@ -943,7 +943,7 @@
     <t>Encounter.class</t>
   </si>
   <si>
-    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques au volet)</t>
+    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques aux cas d'usages)</t>
   </si>
   <si>
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
@@ -959,127 +959,6 @@
   </si>
   <si>
     <t>PV1-2</t>
-  </si>
-  <si>
-    <t>Encounter.class.id</t>
-  </si>
-  <si>
-    <t>Encounter.class.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>Encounter.class.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>Encounter.class.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>Encounter.class.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>Encounter.class.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>Encounter.classHistory</t>
@@ -2230,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN107"/>
+  <dimension ref="A1:AN100"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.34765625" customWidth="true" bestFit="true"/>
@@ -6500,7 +6379,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
@@ -6512,13 +6391,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>281</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>104</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>105</v>
+        <v>306</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6569,19 +6448,19 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>106</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>81</v>
@@ -6598,21 +6477,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>81</v>
@@ -6624,17 +6503,15 @@
         <v>81</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6671,31 +6548,31 @@
         <v>81</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
@@ -6712,21 +6589,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6735,23 +6612,21 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>307</v>
+        <v>111</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>308</v>
+        <v>112</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6799,73 +6674,75 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>313</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6913,39 +6790,39 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>319</v>
+        <v>193</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>320</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6965,21 +6842,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>324</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>81</v>
       </c>
@@ -7003,13 +6878,13 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>81</v>
+        <v>314</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7027,10 +6902,10 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -7045,21 +6920,21 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>326</v>
+        <v>107</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7067,7 +6942,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
@@ -7079,21 +6954,19 @@
         <v>81</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>81</v>
       </c>
@@ -7141,10 +7014,10 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -7159,21 +7032,21 @@
         <v>81</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>334</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7184,7 +7057,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>81</v>
@@ -7196,20 +7069,18 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>336</v>
+        <v>230</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>81</v>
       </c>
@@ -7233,13 +7104,11 @@
         <v>81</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>81</v>
+        <v>322</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7257,13 +7126,13 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>81</v>
@@ -7272,24 +7141,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7300,7 +7169,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7309,16 +7178,16 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7345,13 +7214,13 @@
         <v>81</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>81</v>
+        <v>329</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>81</v>
+        <v>330</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7369,13 +7238,13 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
@@ -7384,7 +7253,7 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>81</v>
+        <v>323</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>107</v>
@@ -7393,15 +7262,15 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7424,13 +7293,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>104</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>105</v>
+        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7457,13 +7326,13 @@
         <v>81</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>81</v>
+        <v>334</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7481,7 +7350,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>106</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7493,38 +7362,38 @@
         <v>81</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>107</v>
+        <v>336</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>109</v>
+        <v>340</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>81</v>
@@ -7533,19 +7402,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>110</v>
+        <v>341</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>111</v>
+        <v>342</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>112</v>
+        <v>343</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>113</v>
+        <v>344</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7595,31 +7464,31 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>117</v>
+        <v>339</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>81</v>
+        <v>345</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>346</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>81</v>
+        <v>347</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48">
@@ -7631,7 +7500,7 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7644,26 +7513,22 @@
         <v>81</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>110</v>
+        <v>350</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>289</v>
+        <v>351</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>81</v>
       </c>
@@ -7711,7 +7576,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7723,38 +7588,38 @@
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>81</v>
+        <v>354</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>81</v>
+        <v>357</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7766,13 +7631,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>148</v>
+        <v>358</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7799,13 +7664,13 @@
         <v>81</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>353</v>
+        <v>81</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>354</v>
+        <v>81</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>81</v>
@@ -7823,13 +7688,13 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
@@ -7838,10 +7703,10 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>81</v>
+        <v>361</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>107</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7852,10 +7717,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7863,10 +7728,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7875,16 +7740,16 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7935,13 +7800,13 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
@@ -7950,24 +7815,24 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>107</v>
+        <v>367</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>81</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7978,7 +7843,7 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -7987,20 +7852,18 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8025,11 +7888,13 @@
         <v>81</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>81</v>
@@ -8047,50 +7912,50 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>358</v>
+        <v>106</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>364</v>
+        <v>107</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>302</v>
+        <v>81</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>365</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>81</v>
@@ -8099,18 +7964,20 @@
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>367</v>
+        <v>111</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -8135,13 +8002,13 @@
         <v>81</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>369</v>
+        <v>81</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>370</v>
+        <v>81</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>81</v>
@@ -8159,22 +8026,22 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>366</v>
+        <v>117</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>107</v>
@@ -8183,47 +8050,51 @@
         <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>371</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>373</v>
+        <v>289</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8247,13 +8118,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>374</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8271,50 +8142,50 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>372</v>
+        <v>291</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>376</v>
+        <v>193</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>377</v>
+        <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>378</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
@@ -8326,16 +8197,16 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>381</v>
+        <v>230</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8361,13 +8232,13 @@
         <v>81</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>81</v>
+        <v>374</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8385,13 +8256,13 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
@@ -8400,24 +8271,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>387</v>
+        <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>388</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8428,7 +8299,7 @@
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8437,16 +8308,16 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>390</v>
+        <v>256</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8497,13 +8368,13 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
@@ -8512,35 +8383,35 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>107</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>397</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8549,16 +8420,16 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8609,13 +8480,13 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
@@ -8624,24 +8495,24 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>81</v>
+        <v>391</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>81</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8664,13 +8535,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8721,7 +8592,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8736,24 +8607,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>406</v>
+        <v>361</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8761,7 +8632,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -8776,15 +8647,17 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>103</v>
+        <v>256</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>104</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8833,7 +8706,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>106</v>
+        <v>399</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8845,38 +8718,38 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>107</v>
+        <v>404</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>81</v>
+        <v>405</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>81</v>
@@ -8888,16 +8761,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>110</v>
+        <v>408</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>111</v>
+        <v>409</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>112</v>
+        <v>410</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>113</v>
+        <v>411</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8947,43 +8820,43 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>117</v>
+        <v>407</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>81</v>
+        <v>403</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>107</v>
+        <v>412</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>81</v>
+        <v>413</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>288</v>
+        <v>415</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8996,26 +8869,24 @@
         <v>81</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>289</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>290</v>
+        <v>417</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
       </c>
@@ -9039,13 +8910,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>81</v>
+        <v>420</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9063,7 +8934,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>291</v>
+        <v>414</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9075,31 +8946,31 @@
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>81</v>
+        <v>421</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>193</v>
+        <v>422</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>81</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>81</v>
+        <v>415</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9118,16 +8989,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>230</v>
+        <v>426</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9153,13 +9024,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>414</v>
+        <v>81</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -9177,7 +9048,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9192,24 +9063,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9220,7 +9091,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9229,16 +9100,16 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9289,13 +9160,13 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
@@ -9307,21 +9178,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>424</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9341,16 +9212,16 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>427</v>
+        <v>104</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>428</v>
+        <v>105</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9401,7 +9272,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>425</v>
+        <v>106</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9413,19 +9284,19 @@
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>430</v>
+        <v>107</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>432</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64">
@@ -9437,7 +9308,7 @@
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9453,18 +9324,20 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>435</v>
+        <v>111</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9513,7 +9386,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>433</v>
+        <v>117</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9525,61 +9398,63 @@
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>401</v>
+        <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>437</v>
+        <v>107</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>438</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>256</v>
+        <v>110</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>440</v>
+        <v>289</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>441</v>
+        <v>290</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
       </c>
@@ -9627,47 +9502,47 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>439</v>
+        <v>291</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>443</v>
+        <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>444</v>
+        <v>193</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>445</v>
+        <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>436</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -9679,19 +9554,19 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9741,10 +9616,10 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
@@ -9756,35 +9631,35 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>81</v>
+        <v>423</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>81</v>
@@ -9793,20 +9668,18 @@
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>230</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -9834,10 +9707,10 @@
         <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9855,13 +9728,13 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
@@ -9870,35 +9743,35 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>462</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -9907,20 +9780,18 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -9969,13 +9840,13 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
@@ -9984,24 +9855,24 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>461</v>
+        <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10012,7 +9883,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10021,18 +9892,20 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>281</v>
+        <v>454</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10081,7 +9954,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10099,7 +9972,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -10110,10 +9983,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10136,15 +10009,17 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>103</v>
+        <v>281</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>104</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10193,7 +10068,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>106</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10205,13 +10080,13 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>463</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -10222,21 +10097,21 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10248,17 +10123,15 @@
         <v>81</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10307,19 +10180,19 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>81</v>
@@ -10336,14 +10209,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>288</v>
+        <v>109</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10356,26 +10229,24 @@
         <v>81</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>289</v>
+        <v>111</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>290</v>
+        <v>112</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O72" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>81</v>
       </c>
@@ -10423,7 +10294,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>291</v>
+        <v>117</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10441,7 +10312,7 @@
         <v>81</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>81</v>
@@ -10452,44 +10323,46 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>476</v>
+        <v>288</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>477</v>
+        <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>478</v>
+        <v>289</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>479</v>
+        <v>290</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>81</v>
       </c>
@@ -10537,39 +10410,39 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>291</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>480</v>
+        <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>481</v>
+        <v>193</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10592,13 +10465,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10625,13 +10498,13 @@
         <v>81</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>487</v>
+        <v>81</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>81</v>
@@ -10649,7 +10522,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10667,21 +10540,21 @@
         <v>81</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>81</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10704,13 +10577,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>489</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>490</v>
+        <v>104</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>491</v>
+        <v>105</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10761,7 +10634,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10773,13 +10646,13 @@
         <v>81</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>492</v>
+        <v>107</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>
@@ -10790,21 +10663,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>81</v>
@@ -10816,16 +10689,16 @@
         <v>81</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>494</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>495</v>
+        <v>111</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>496</v>
+        <v>112</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>497</v>
+        <v>113</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10863,19 +10736,19 @@
         <v>81</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>493</v>
+        <v>117</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -10887,13 +10760,13 @@
         <v>81</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>498</v>
+        <v>107</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>81</v>
@@ -10904,10 +10777,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10924,24 +10797,26 @@
         <v>81</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>281</v>
+        <v>170</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>501</v>
+        <v>221</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
       </c>
@@ -10965,13 +10840,13 @@
         <v>81</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
@@ -10989,7 +10864,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>499</v>
+        <v>227</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11007,21 +10882,21 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>503</v>
+        <v>228</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>81</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11029,7 +10904,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11041,19 +10916,23 @@
         <v>81</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>231</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
       </c>
@@ -11077,13 +10956,11 @@
         <v>81</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>81</v>
@@ -11101,7 +10978,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>236</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11113,38 +10990,38 @@
         <v>81</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>81</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>505</v>
+        <v>476</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>505</v>
+        <v>476</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>81</v>
@@ -11153,33 +11030,35 @@
         <v>81</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
+        <v>477</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>81</v>
+        <v>478</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>81</v>
@@ -11215,75 +11094,73 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>244</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>107</v>
+        <v>245</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>506</v>
+        <v>479</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>288</v>
+        <v>81</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J80" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>81</v>
       </c>
@@ -11295,7 +11172,7 @@
         <v>81</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>81</v>
+        <v>251</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>81</v>
@@ -11331,39 +11208,39 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>81</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>507</v>
+        <v>480</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11383,16 +11260,16 @@
         <v>81</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>508</v>
+        <v>257</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>509</v>
+        <v>258</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11443,7 +11320,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>507</v>
+        <v>259</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11461,21 +11338,21 @@
         <v>81</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>510</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>511</v>
+        <v>481</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11495,18 +11372,20 @@
         <v>81</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>263</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>104</v>
+        <v>264</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -11555,7 +11434,7 @@
         <v>81</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>106</v>
+        <v>267</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11567,38 +11446,38 @@
         <v>81</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>107</v>
+        <v>268</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>81</v>
+        <v>269</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>81</v>
@@ -11610,17 +11489,15 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>110</v>
+        <v>483</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>111</v>
+        <v>484</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>81</v>
@@ -11657,37 +11534,37 @@
         <v>81</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>117</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>107</v>
+        <v>486</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -11698,10 +11575,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11718,26 +11595,22 @@
         <v>81</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>220</v>
+        <v>488</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>81</v>
       </c>
@@ -11763,11 +11636,9 @@
       <c r="X84" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="Y84" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>226</v>
+        <v>490</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11785,7 +11656,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>227</v>
+        <v>487</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11803,21 +11674,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>228</v>
+        <v>491</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>193</v>
+        <v>492</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11825,7 +11696,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>89</v>
@@ -11837,23 +11708,19 @@
         <v>81</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>231</v>
+        <v>494</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>81</v>
       </c>
@@ -11877,11 +11744,13 @@
         <v>81</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>235</v>
+        <v>497</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11899,7 +11768,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>236</v>
+        <v>493</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11917,21 +11786,21 @@
         <v>81</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>228</v>
+        <v>107</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>237</v>
+        <v>498</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11939,10 +11808,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>81</v>
@@ -11951,35 +11820,35 @@
         <v>81</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>131</v>
+        <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>239</v>
+        <v>500</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>241</v>
+        <v>502</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>242</v>
+        <v>503</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>518</v>
+        <v>81</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>81</v>
@@ -11991,13 +11860,13 @@
         <v>81</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>81</v>
+        <v>504</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>81</v>
+        <v>505</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -12015,13 +11884,13 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>244</v>
+        <v>499</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>81</v>
@@ -12033,21 +11902,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>245</v>
+        <v>506</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>246</v>
+        <v>507</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12055,10 +11924,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>81</v>
@@ -12067,20 +11936,18 @@
         <v>81</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>248</v>
+        <v>509</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>81</v>
@@ -12093,7 +11960,7 @@
         <v>81</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>81</v>
@@ -12105,13 +11972,13 @@
         <v>81</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>81</v>
+        <v>511</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>81</v>
@@ -12129,13 +11996,13 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>252</v>
+        <v>508</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>81</v>
@@ -12147,21 +12014,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>253</v>
+        <v>513</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>254</v>
+        <v>514</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12172,7 +12039,7 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>81</v>
@@ -12181,16 +12048,16 @@
         <v>81</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>257</v>
+        <v>516</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>258</v>
+        <v>517</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12217,13 +12084,13 @@
         <v>81</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>81</v>
+        <v>519</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12241,13 +12108,13 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>259</v>
+        <v>515</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>81</v>
@@ -12259,21 +12126,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>261</v>
+        <v>521</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12293,20 +12160,18 @@
         <v>81</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>263</v>
+        <v>483</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>264</v>
+        <v>523</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12355,7 +12220,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>267</v>
+        <v>522</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12373,21 +12238,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>268</v>
+        <v>525</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>269</v>
+        <v>526</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12410,13 +12275,13 @@
         <v>81</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>523</v>
+        <v>230</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12443,13 +12308,11 @@
         <v>81</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>81</v>
+        <v>530</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12467,7 +12330,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12485,21 +12348,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12522,15 +12385,17 @@
         <v>81</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -12555,11 +12420,13 @@
         <v>81</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>81</v>
@@ -12577,13 +12444,13 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>81</v>
@@ -12595,21 +12462,21 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>532</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12632,13 +12499,13 @@
         <v>81</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>535</v>
+        <v>105</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12665,13 +12532,13 @@
         <v>81</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>536</v>
+        <v>81</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>537</v>
+        <v>81</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>81</v>
@@ -12689,7 +12556,7 @@
         <v>81</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>533</v>
+        <v>106</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12701,7 +12568,7 @@
         <v>81</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>81</v>
@@ -12713,7 +12580,7 @@
         <v>81</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>538</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93">
@@ -12725,7 +12592,7 @@
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12744,20 +12611,18 @@
         <v>81</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>540</v>
+        <v>111</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>541</v>
+        <v>112</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>81</v>
       </c>
@@ -12781,13 +12646,13 @@
         <v>81</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>544</v>
+        <v>81</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>545</v>
+        <v>81</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>81</v>
@@ -12805,7 +12670,7 @@
         <v>81</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>539</v>
+        <v>117</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12817,31 +12682,31 @@
         <v>81</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>546</v>
+        <v>107</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>547</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>81</v>
+        <v>288</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12854,22 +12719,26 @@
         <v>81</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>549</v>
+        <v>289</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>81</v>
       </c>
@@ -12893,13 +12762,13 @@
         <v>81</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>551</v>
+        <v>81</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>552</v>
+        <v>81</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>81</v>
@@ -12917,7 +12786,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>548</v>
+        <v>291</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12929,27 +12798,27 @@
         <v>81</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>553</v>
+        <v>193</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12957,10 +12826,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>81</v>
@@ -12972,13 +12841,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>230</v>
+        <v>542</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>556</v>
+        <v>543</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13005,13 +12874,13 @@
         <v>81</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>174</v>
+        <v>81</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>558</v>
+        <v>81</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>559</v>
+        <v>81</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>81</v>
@@ -13029,13 +12898,13 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>81</v>
@@ -13044,24 +12913,24 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>81</v>
+        <v>545</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>560</v>
+        <v>390</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>81</v>
+        <v>546</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>561</v>
+        <v>547</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13084,15 +12953,17 @@
         <v>81</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>523</v>
+        <v>170</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N96" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>81</v>
@@ -13117,13 +12988,13 @@
         <v>81</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>81</v>
+        <v>552</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>81</v>
+        <v>553</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13141,7 +13012,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13159,21 +13030,21 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>566</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13199,12 +13070,14 @@
         <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>81</v>
@@ -13233,7 +13106,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13251,7 +13124,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13269,21 +13142,21 @@
         <v>81</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>571</v>
+        <v>81</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>572</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13306,17 +13179,15 @@
         <v>81</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>281</v>
+        <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>81</v>
@@ -13365,13 +13236,13 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>81</v>
@@ -13383,7 +13254,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>577</v>
+        <v>383</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13394,10 +13265,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13420,13 +13291,13 @@
         <v>81</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>103</v>
+        <v>263</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>104</v>
+        <v>564</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>105</v>
+        <v>565</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13477,7 +13348,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>106</v>
+        <v>563</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13489,38 +13360,38 @@
         <v>81</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>81</v>
+        <v>389</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>107</v>
+        <v>566</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>81</v>
+        <v>567</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>81</v>
@@ -13532,16 +13403,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>110</v>
+        <v>569</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>111</v>
+        <v>570</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>112</v>
+        <v>571</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>113</v>
+        <v>572</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13591,822 +13462,30 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>117</v>
+        <v>568</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>81</v>
+        <v>573</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>107</v>
+        <v>574</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y104" s="2"/>
-      <c r="Z104" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN107" t="s" s="2">
         <v>81</v>
       </c>
     </row>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="574">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:39:39+00:00</t>
+    <t>2026-07-21T11:52:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -943,13 +943,22 @@
     <t>Encounter.class</t>
   </si>
   <si>
-    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques aux cas d'usages)</t>
+    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques aux cas d'usages)
+Exemples de codes les plus courants (http://terminology.hl7.org/CodeSystem/v3-ActCode) :
+- ACUTE : Inpatient acute
+- NONAC : Inpatient non acute
+- PRENC : Pre-admission
+- SS : Short stay
+- VR : Virtual</t>
   </si>
   <si>
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-class|2.2.0</t>
+    <t>Classification of the encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -986,12 +995,6 @@
   </si>
   <si>
     <t>inpatient | outpatient | ambulatory | emergency +.</t>
-  </si>
-  <si>
-    <t>Classification of the encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -1541,7 +1544,7 @@
     <t>From where patient was admitted (physician referral, transfer).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-entree-cisis|20260420150251</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-entree-cisis|20260619134043</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -6316,9 +6319,11 @@
       <c r="X37" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y37" s="2"/>
+      <c r="Y37" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6354,21 +6359,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6394,10 +6399,10 @@
         <v>281</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6448,7 +6453,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6477,10 +6482,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6589,10 +6594,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6703,10 +6708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6819,10 +6824,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6848,10 +6853,10 @@
         <v>148</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6881,10 +6886,10 @@
         <v>152</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6902,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>89</v>
@@ -6931,10 +6936,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6960,10 +6965,10 @@
         <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7014,7 +7019,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>89</v>
@@ -7043,10 +7048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7072,13 +7077,13 @@
         <v>230</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7108,7 +7113,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7126,7 +7131,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7141,24 +7146,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7184,10 +7189,10 @@
         <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7217,11 +7222,11 @@
         <v>160</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>330</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7238,7 +7243,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7253,7 +7258,7 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>107</v>
@@ -7262,15 +7267,15 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7296,10 +7301,10 @@
         <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7329,11 +7334,11 @@
         <v>160</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7350,7 +7355,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7368,25 +7373,25 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7405,16 +7410,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7464,7 +7469,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7479,24 +7484,24 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>348</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7519,13 +7524,13 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7576,7 +7581,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7591,28 +7596,28 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7631,13 +7636,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7688,7 +7693,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7703,10 +7708,10 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7717,10 +7722,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7746,10 +7751,10 @@
         <v>281</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7800,7 +7805,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7815,24 +7820,24 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7941,10 +7946,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8055,10 +8060,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8171,10 +8176,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8200,13 +8205,13 @@
         <v>230</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8235,10 +8240,10 @@
         <v>152</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8256,7 +8261,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8271,24 +8276,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8314,10 +8319,10 @@
         <v>256</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8368,7 +8373,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8386,21 +8391,21 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8423,13 +8428,13 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8480,7 +8485,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8495,24 +8500,24 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8535,13 +8540,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8592,7 +8597,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8607,24 +8612,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>398</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8650,13 +8655,13 @@
         <v>256</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8706,7 +8711,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8721,24 +8726,24 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AM58" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8761,16 +8766,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8820,7 +8825,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8835,28 +8840,28 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8878,13 +8883,13 @@
         <v>230</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8913,11 +8918,11 @@
         <v>174</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z60" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
       </c>
@@ -8934,7 +8939,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8949,28 +8954,28 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8989,16 +8994,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L61" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="M61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9048,7 +9053,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9063,24 +9068,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9106,10 +9111,10 @@
         <v>281</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9160,7 +9165,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9178,7 +9183,7 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
@@ -9189,10 +9194,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9301,10 +9306,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9415,10 +9420,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9531,14 +9536,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9557,16 +9562,16 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="N66" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9616,7 +9621,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>89</v>
@@ -9631,24 +9636,24 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9674,10 +9679,10 @@
         <v>230</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9707,11 +9712,11 @@
         <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
       </c>
@@ -9728,7 +9733,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9757,10 +9762,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9783,13 +9788,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9840,7 +9845,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9858,7 +9863,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9869,10 +9874,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9895,16 +9900,16 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9954,7 +9959,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9972,7 +9977,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -9983,10 +9988,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10012,13 +10017,13 @@
         <v>281</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10068,7 +10073,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10086,7 +10091,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -10097,10 +10102,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10209,10 +10214,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10323,10 +10328,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10439,10 +10444,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10468,10 +10473,10 @@
         <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10522,7 +10527,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10546,15 +10551,15 @@
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10663,10 +10668,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10777,10 +10782,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10893,10 +10898,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10925,7 +10930,7 @@
         <v>231</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>233</v>
@@ -11007,10 +11012,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11039,7 +11044,7 @@
         <v>239</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>241</v>
@@ -11052,7 +11057,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>81</v>
@@ -11123,10 +11128,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11237,10 +11242,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11349,10 +11354,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11463,10 +11468,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11489,13 +11494,13 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L83" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="M83" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11546,7 +11551,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11564,7 +11569,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -11575,10 +11580,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11604,10 +11609,10 @@
         <v>230</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11638,7 +11643,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11656,7 +11661,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11674,21 +11679,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11714,10 +11719,10 @@
         <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11747,11 +11752,11 @@
         <v>160</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>497</v>
-      </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
       </c>
@@ -11768,7 +11773,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11792,15 +11797,15 @@
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11826,16 +11831,16 @@
         <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -11863,11 +11868,11 @@
         <v>160</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="Z86" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="Z86" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
       </c>
@@ -11884,7 +11889,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11902,21 +11907,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11942,10 +11947,10 @@
         <v>230</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11975,11 +11980,11 @@
         <v>174</v>
       </c>
       <c r="Y87" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="Z87" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="Z87" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AA87" t="s" s="2">
         <v>81</v>
       </c>
@@ -11996,7 +12001,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12014,21 +12019,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN87" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>514</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12054,10 +12059,10 @@
         <v>230</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12087,11 +12092,11 @@
         <v>174</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12108,7 +12113,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12126,21 +12131,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>521</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12163,13 +12168,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12220,7 +12225,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12238,21 +12243,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN89" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>526</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12278,10 +12283,10 @@
         <v>230</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12312,7 +12317,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12335,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12348,21 +12353,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>532</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12388,13 +12393,13 @@
         <v>281</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12444,7 +12449,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12462,7 +12467,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12473,10 +12478,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12585,10 +12590,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12699,10 +12704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12815,10 +12820,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12841,13 +12846,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12898,7 +12903,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>89</v>
@@ -12913,24 +12918,24 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AL95" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>547</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12956,13 +12961,13 @@
         <v>170</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12991,11 +12996,11 @@
         <v>224</v>
       </c>
       <c r="Y96" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="Z96" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>553</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
       </c>
@@ -13012,7 +13017,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13030,7 +13035,7 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
@@ -13041,10 +13046,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13070,13 +13075,13 @@
         <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="N97" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13106,7 +13111,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13124,7 +13129,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13153,10 +13158,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13182,10 +13187,10 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13236,7 +13241,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13254,7 +13259,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13265,10 +13270,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13294,10 +13299,10 @@
         <v>263</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13348,7 +13353,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13363,24 +13368,24 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AL99" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN99" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>567</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13403,16 +13408,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13462,7 +13467,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13477,10 +13482,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AL100" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T11:52:46+00:00</t>
+    <t>2026-07-21T11:54:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -943,13 +943,7 @@
     <t>Encounter.class</t>
   </si>
   <si>
-    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques aux cas d'usages)
-Exemples de codes les plus courants (http://terminology.hl7.org/CodeSystem/v3-ActCode) :
-- ACUTE : Inpatient acute
-- NONAC : Inpatient non acute
-- PRENC : Pre-admission
-- SS : Short stay
-- VR : Virtual</t>
+    <t>Type de rencontre (codes HL7 ActEncounterCode ou codes spécifiques aux cas d'usages) — exemples les plus courants (v3-ActCode) : ACUTE (Inpatient acute), NONAC (Inpatient non acute), PRENC (Pre-admission), SS (Short stay), VR (Virtual)</t>
   </si>
   <si>
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
@@ -1051,9 +1045,7 @@
     <t>Encounter.priority</t>
   </si>
   <si>
-    <t>Si la rencontre est prévue non confirmée et qu'une confirmation est attendue :
-code='CS', display='callback for scheduling'
-Sinon, l'élément 'priority' n'est pas fourni.</t>
+    <t>Si la rencontre est prévue non confirmée et qu'une confirmation est attendue : code='CS', display='callback for scheduling'. Sinon, l'élément 'priority' n'est pas fourni.</t>
   </si>
   <si>
     <t>Indicates the urgency of the encounter.</t>
@@ -1261,9 +1253,7 @@
     <t>Encounter.period</t>
   </si>
   <si>
-    <t>Date début et fin de la rencontre
-Si la rencontre est réalisée ou planifiée : la date est obligatoire.
-Si la rencontre est prévue non confirmée : la date est facultative.</t>
+    <t>Date début et fin de la rencontre. Si la rencontre est réalisée ou planifiée : la date est obligatoire. Si la rencontre est prévue non confirmée : la date est facultative.</t>
   </si>
   <si>
     <t>The start and end time of the encounter.</t>
@@ -1658,8 +1648,7 @@
     <t>Encounter.hospitalization.dischargeDisposition</t>
   </si>
   <si>
-    <t>Modalité de sortie du patient lors de la rencontre:
-Valeur provenant du jdv-modalite-sortie-cisis ou autre JDV spécifique au volet</t>
+    <t>Modalité de sortie du patient lors de la rencontre : valeur provenant du jdv-modalite-sortie-cisis ou autre JDV spécifique au volet</t>
   </si>
   <si>
     <t>Category or kind of location after discharge.</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T11:54:41+00:00</t>
+    <t>2026-07-21T12:00:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="575">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:00:27+00:00</t>
+    <t>2026-07-27T13:17:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -949,46 +949,49 @@
     <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActEncounterCode-cisis|20260619134042</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>PV1-2</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory</t>
+  </si>
+  <si>
+    <t>List of past encounter classes</t>
+  </si>
+  <si>
+    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.id</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.extension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.class</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +.</t>
+  </si>
+  <si>
     <t>Classification of the encounter.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>PV1-2</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory</t>
-  </si>
-  <si>
-    <t>List of past encounter classes</t>
-  </si>
-  <si>
-    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.id</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.class</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +.</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -2129,7 +2132,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.6875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.1640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6308,11 +6311,9 @@
       <c r="X37" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Y37" t="s" s="2">
+      <c r="Y37" s="2"/>
+      <c r="Z37" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6348,21 +6349,21 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6388,10 +6389,10 @@
         <v>281</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6442,7 +6443,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6471,10 +6472,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6583,10 +6584,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6697,10 +6698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6813,10 +6814,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6842,10 +6843,10 @@
         <v>148</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6875,10 +6876,10 @@
         <v>152</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -6896,7 +6897,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>89</v>
@@ -6925,10 +6926,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6954,10 +6955,10 @@
         <v>256</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7008,7 +7009,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>89</v>
@@ -7037,10 +7038,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7066,13 +7067,13 @@
         <v>230</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7102,7 +7103,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>81</v>
@@ -7120,7 +7121,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7135,24 +7136,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7178,10 +7179,10 @@
         <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7211,10 +7212,10 @@
         <v>160</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>81</v>
@@ -7232,7 +7233,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7247,7 +7248,7 @@
         <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>107</v>
@@ -7256,15 +7257,15 @@
         <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7290,10 +7291,10 @@
         <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7323,10 +7324,10 @@
         <v>160</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>81</v>
@@ -7344,7 +7345,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7362,25 +7363,25 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7399,16 +7400,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7458,7 +7459,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7473,24 +7474,24 @@
         <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7513,13 +7514,13 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7570,7 +7571,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7585,28 +7586,28 @@
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7625,13 +7626,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7682,7 +7683,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7697,10 +7698,10 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>81</v>
@@ -7711,10 +7712,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7740,10 +7741,10 @@
         <v>281</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7794,7 +7795,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7809,24 +7810,24 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7935,10 +7936,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8049,10 +8050,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8165,10 +8166,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8194,13 +8195,13 @@
         <v>230</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8229,10 +8230,10 @@
         <v>152</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>81</v>
@@ -8250,7 +8251,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8265,24 +8266,24 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8308,10 +8309,10 @@
         <v>256</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8362,7 +8363,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8380,21 +8381,21 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8417,13 +8418,13 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8474,7 +8475,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8489,24 +8490,24 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8529,13 +8530,13 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8586,7 +8587,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8601,24 +8602,24 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8644,13 +8645,13 @@
         <v>256</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8700,7 +8701,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8715,24 +8716,24 @@
         <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8755,16 +8756,16 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8814,7 +8815,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8829,28 +8830,28 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8872,13 +8873,13 @@
         <v>230</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8907,10 +8908,10 @@
         <v>174</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8928,7 +8929,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8943,28 +8944,28 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8983,16 +8984,16 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9042,7 +9043,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9057,24 +9058,24 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9100,10 +9101,10 @@
         <v>281</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9154,7 +9155,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9172,7 +9173,7 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
@@ -9183,10 +9184,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9295,10 +9296,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9409,10 +9410,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9525,14 +9526,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9551,16 +9552,16 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9610,7 +9611,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>89</v>
@@ -9625,24 +9626,24 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9668,10 +9669,10 @@
         <v>230</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9701,10 +9702,10 @@
         <v>174</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
@@ -9722,7 +9723,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9751,10 +9752,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9777,13 +9778,13 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9834,7 +9835,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9852,7 +9853,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9863,10 +9864,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9889,16 +9890,16 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9948,7 +9949,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9966,7 +9967,7 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>81</v>
@@ -9977,10 +9978,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10006,13 +10007,13 @@
         <v>281</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10062,7 +10063,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10080,7 +10081,7 @@
         <v>81</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>81</v>
@@ -10091,10 +10092,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10203,10 +10204,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10317,10 +10318,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10433,10 +10434,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10462,10 +10463,10 @@
         <v>210</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10516,7 +10517,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10540,15 +10541,15 @@
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10657,10 +10658,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10771,10 +10772,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10887,10 +10888,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10919,7 +10920,7 @@
         <v>231</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>233</v>
@@ -11001,10 +11002,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11033,7 +11034,7 @@
         <v>239</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>241</v>
@@ -11046,7 +11047,7 @@
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>81</v>
@@ -11117,10 +11118,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11231,10 +11232,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11343,10 +11344,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11457,10 +11458,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11483,13 +11484,13 @@
         <v>81</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11540,7 +11541,7 @@
         <v>81</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11558,7 +11559,7 @@
         <v>81</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>81</v>
@@ -11569,10 +11570,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11598,10 +11599,10 @@
         <v>230</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11632,7 +11633,7 @@
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11650,7 +11651,7 @@
         <v>81</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11668,21 +11669,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11708,10 +11709,10 @@
         <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11741,10 +11742,10 @@
         <v>160</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11762,7 +11763,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11786,15 +11787,15 @@
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11820,16 +11821,16 @@
         <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -11857,10 +11858,10 @@
         <v>160</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -11878,7 +11879,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11896,21 +11897,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11936,10 +11937,10 @@
         <v>230</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11969,10 +11970,10 @@
         <v>174</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>81</v>
@@ -11990,7 +11991,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12008,21 +12009,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12048,10 +12049,10 @@
         <v>230</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12081,10 +12082,10 @@
         <v>174</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12102,7 +12103,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12120,21 +12121,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12157,13 +12158,13 @@
         <v>81</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12214,7 +12215,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12232,21 +12233,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12272,10 +12273,10 @@
         <v>230</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12306,7 +12307,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12324,7 +12325,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12342,21 +12343,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12382,13 +12383,13 @@
         <v>281</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12438,7 +12439,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12456,7 +12457,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12467,10 +12468,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12579,10 +12580,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12693,10 +12694,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12809,10 +12810,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12835,13 +12836,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12892,7 +12893,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>89</v>
@@ -12907,24 +12908,24 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12950,13 +12951,13 @@
         <v>170</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12985,10 +12986,10 @@
         <v>224</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13006,7 +13007,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13024,7 +13025,7 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
@@ -13035,10 +13036,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13064,13 +13065,13 @@
         <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13100,7 +13101,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13118,7 +13119,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13147,10 +13148,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13176,10 +13177,10 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13230,7 +13231,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13248,7 +13249,7 @@
         <v>81</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>81</v>
@@ -13259,10 +13260,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13288,10 +13289,10 @@
         <v>263</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13342,7 +13343,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13357,24 +13358,24 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13397,16 +13398,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13456,7 +13457,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13471,10 +13472,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:17:31+00:00</t>
+    <t>2026-07-27T13:23:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1048,7 +1048,7 @@
     <t>Encounter.priority</t>
   </si>
   <si>
-    <t>Si la rencontre est prévue non confirmée et qu'une confirmation est attendue : code='CS', display='callback for scheduling'. Sinon, l'élément 'priority' n'est pas fourni.</t>
+    <t>Indicates the urgency of the encounter</t>
   </si>
   <si>
     <t>Indicates the urgency of the encounter.</t>
@@ -1146,7 +1146,7 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>Liste des participants impliqués dans la rencontre</t>
+    <t>List of participants involved in the encounter | Liste des personnes impliquées dans la rencontre</t>
   </si>
   <si>
     <t>The list of people responsible for providing the service.</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="576">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:23:52+00:00</t>
+    <t>2026-07-27T13:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1537,7 +1537,10 @@
     <t>From where patient was admitted (physician referral, transfer).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-modalite-entree-cisis|20260619134043</t>
+    <t>From where the patient was admitted.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-admit-source|4.0.1</t>
   </si>
   <si>
     <t>.admissionReferralSourceCode</t>
@@ -8627,7 +8630,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>89</v>
@@ -11629,11 +11632,13 @@
         <v>81</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>81</v>
@@ -11669,21 +11674,21 @@
         <v>81</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11709,10 +11714,10 @@
         <v>230</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11742,10 +11747,10 @@
         <v>160</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>81</v>
@@ -11763,7 +11768,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11787,15 +11792,15 @@
         <v>81</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11821,16 +11826,16 @@
         <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>81</v>
@@ -11858,10 +11863,10 @@
         <v>160</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>81</v>
@@ -11879,7 +11884,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -11897,21 +11902,21 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11937,10 +11942,10 @@
         <v>230</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11970,10 +11975,10 @@
         <v>174</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>81</v>
@@ -11991,7 +11996,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12009,21 +12014,21 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12049,10 +12054,10 @@
         <v>230</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12082,10 +12087,10 @@
         <v>174</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
@@ -12103,7 +12108,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12121,21 +12126,21 @@
         <v>81</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12161,10 +12166,10 @@
         <v>483</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12215,7 +12220,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12233,21 +12238,21 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12273,10 +12278,10 @@
         <v>230</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12307,7 +12312,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12325,7 +12330,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12343,21 +12348,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12383,13 +12388,13 @@
         <v>281</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12439,7 +12444,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12457,7 +12462,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12468,10 +12473,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12580,10 +12585,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12694,10 +12699,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12810,10 +12815,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12836,13 +12841,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12893,7 +12898,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>89</v>
@@ -12908,24 +12913,24 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>390</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12951,13 +12956,13 @@
         <v>170</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12986,10 +12991,10 @@
         <v>224</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13007,7 +13012,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13025,7 +13030,7 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
@@ -13036,10 +13041,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13065,13 +13070,13 @@
         <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13101,7 +13106,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13119,7 +13124,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13148,10 +13153,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13177,10 +13182,10 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13231,7 +13236,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13260,10 +13265,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13289,10 +13294,10 @@
         <v>263</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13343,7 +13348,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13361,21 +13366,21 @@
         <v>389</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13398,16 +13403,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13457,7 +13462,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13472,10 +13477,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:42:38+00:00</t>
+    <t>2026-07-27T13:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1654,7 +1654,7 @@
     <t>Encounter.hospitalization.dischargeDisposition</t>
   </si>
   <si>
-    <t>Modalité de sortie du patient lors de la rencontre : valeur provenant du jdv-modalite-sortie-cisis ou autre JDV spécifique au volet</t>
+    <t>Modalité de sortie du patient lors de la rencontre.</t>
   </si>
   <si>
     <t>Category or kind of location after discharge.</t>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:52:49+00:00</t>
+    <t>2026-07-27T13:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12373,7 +12373,7 @@
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>81</v>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3609" uniqueCount="577">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:55:37+00:00</t>
+    <t>2026-07-27T16:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1660,7 +1660,10 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
+    <t>Discharge Disposition.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition|4.0.1</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -12310,9 +12313,11 @@
       <c r="X90" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y90" s="2"/>
+      <c r="Y90" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>81</v>
@@ -12348,21 +12353,21 @@
         <v>81</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12388,13 +12393,13 @@
         <v>281</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12444,7 +12449,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12462,7 +12467,7 @@
         <v>81</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>81</v>
@@ -12473,10 +12478,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12585,10 +12590,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12699,10 +12704,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12815,10 +12820,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12841,13 +12846,13 @@
         <v>81</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12898,7 +12903,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>89</v>
@@ -12913,24 +12918,24 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>390</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12956,13 +12961,13 @@
         <v>170</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12991,10 +12996,10 @@
         <v>224</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>81</v>
@@ -13012,7 +13017,7 @@
         <v>81</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13030,7 +13035,7 @@
         <v>81</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>81</v>
@@ -13041,10 +13046,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13070,13 +13075,13 @@
         <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13106,7 +13111,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>81</v>
@@ -13124,7 +13129,7 @@
         <v>81</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13153,10 +13158,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13182,10 +13187,10 @@
         <v>256</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13236,7 +13241,7 @@
         <v>81</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13265,10 +13270,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13294,10 +13299,10 @@
         <v>263</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13348,7 +13353,7 @@
         <v>81</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13366,21 +13371,21 @@
         <v>389</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13403,16 +13408,16 @@
         <v>81</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13462,7 +13467,7 @@
         <v>81</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13477,10 +13482,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>81</v>

--- a/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-doc-core-encounter/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T16:09:25+00:00</t>
+    <t>2026-07-28T08:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1073,7 +1073,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient-ins|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -2123,7 +2123,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="117.0625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="124.91015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
